--- a/数据表/Datas/UIFormConfig_界面配置.xlsx
+++ b/数据表/Datas/UIFormConfig_界面配置.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16080"/>
+    <workbookView windowHeight="16660"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="24">
   <si>
     <t>##var</t>
   </si>
@@ -96,6 +96,9 @@
   </si>
   <si>
     <t>AboutForm</t>
+  </si>
+  <si>
+    <t>BattleForm</t>
   </si>
 </sst>
 </file>
@@ -307,7 +310,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -359,18 +362,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -708,7 +699,7 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -774,90 +765,90 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -879,9 +870,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="7" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1355,8 +1343,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelRow="7" outlineLevelCol="5"/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="13" style="1" customWidth="1"/>
     <col min="2" max="2" width="17.8897058823529" style="1" customWidth="1"/>
@@ -1451,10 +1439,10 @@
       <c r="B5" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="7" t="s">
         <v>19</v>
       </c>
       <c r="E5" s="7" t="b">
@@ -1469,10 +1457,10 @@
       <c r="B6" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="7" t="s">
         <v>19</v>
       </c>
       <c r="E6" s="7" t="b">
@@ -1487,10 +1475,10 @@
       <c r="B7" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="7" t="s">
         <v>19</v>
       </c>
       <c r="E7" s="7" t="b">
@@ -1505,16 +1493,33 @@
       <c r="B8" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="7" t="s">
         <v>19</v>
       </c>
       <c r="E8" s="7" t="b">
         <v>0</v>
       </c>
       <c r="F8" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:6">
+      <c r="B9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" s="7" t="b">
         <v>1</v>
       </c>
     </row>

--- a/数据表/Datas/UIFormConfig_界面配置.xlsx
+++ b/数据表/Datas/UIFormConfig_界面配置.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\Seek-Battle-Evacuate\数据表\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="16660"/>
+    <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="27">
   <si>
     <t>##var</t>
   </si>
@@ -68,19 +73,59 @@
     <t>##</t>
   </si>
   <si>
-    <t>界面编号</t>
-  </si>
-  <si>
-    <t>资源名称</t>
-  </si>
-  <si>
-    <t>界面组名称</t>
-  </si>
-  <si>
-    <t>是否允许多个界面实例</t>
-  </si>
-  <si>
-    <t>是否暂停被其覆盖的界面</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>界面编号</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>资源名称</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>界面组名称</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>是否允许多个界面实例</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>是否暂停被其覆盖的界面</t>
+    </r>
   </si>
   <si>
     <t>DialogForm</t>
@@ -99,6 +144,15 @@
   </si>
   <si>
     <t>BattleForm</t>
+  </si>
+  <si>
+    <t>Battle</t>
+  </si>
+  <si>
+    <t>JoystickForm</t>
+  </si>
+  <si>
+    <t>Input</t>
   </si>
 </sst>
 </file>
@@ -119,43 +173,37 @@
     </font>
     <font>
       <sz val="12"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF006100"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF1F4E78"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF595959"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF9C0006"/>
-      <name val="Andale Mono"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF9C0006"/>
-      <name val="PingFang SC Regular"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF202020"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
@@ -308,6 +356,12 @@
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="35">
@@ -702,153 +756,153 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -863,13 +917,10 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1343,11 +1394,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="13" style="1" customWidth="1"/>
-    <col min="2" max="2" width="17.8897058823529" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.8916666666667" style="1" customWidth="1"/>
     <col min="3" max="4" width="22" style="1" customWidth="1"/>
     <col min="5" max="5" width="26" style="1" customWidth="1"/>
     <col min="6" max="6" width="30" style="1" customWidth="1"/>
@@ -1418,91 +1469,91 @@
       <c r="A4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="5" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:6">
-      <c r="A5" s="7"/>
-      <c r="B5" s="8" t="s">
+      <c r="A5" s="6"/>
+      <c r="B5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="7" t="b">
+      <c r="E5" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="F5" s="7" t="b">
+      <c r="F5" s="6" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:6">
-      <c r="A6" s="7"/>
-      <c r="B6" s="8" t="s">
+      <c r="A6" s="6"/>
+      <c r="B6" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="7" t="b">
+      <c r="E6" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="F6" s="7" t="b">
+      <c r="F6" s="6" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:6">
-      <c r="A7" s="7"/>
-      <c r="B7" s="8" t="s">
+      <c r="A7" s="6"/>
+      <c r="B7" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="7" t="b">
+      <c r="E7" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="F7" s="7" t="b">
+      <c r="F7" s="6" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:6">
-      <c r="A8" s="7"/>
-      <c r="B8" s="8" t="s">
+      <c r="A8" s="6"/>
+      <c r="B8" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="7" t="b">
+      <c r="E8" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="F8" s="7" t="b">
+      <c r="F8" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1513,14 +1564,31 @@
       <c r="C9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="7" t="b">
+      <c r="D9" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="F9" s="7" t="b">
+      <c r="F9" s="6" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:6">
+      <c r="B10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" s="6" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
